--- a/docs/page-copy/04-视频目录-灵魂档案.xlsx
+++ b/docs/page-copy/04-视频目录-灵魂档案.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G73"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -686,10 +686,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D13" t="str">
-        <v>When Woos record of Soul were filmed, Spirits were sometimes called ghost and sometimes soul, but in the spirit medicine filmed in 2025, ghosts were clearly called spirit(ghost).</v>
+        <v>When Wu's Spirit Files were filmed, spirit, spirit (ghost), and spirit (soul) were not strictly distinguished and were used interchangeably. In Wu's Soul Medicine filmed in 2025, the three terms were formally defined. Spirit refers to the soul-body while a person is alive. Spirit (ghost) refers to the independent soul-life separated from the physical body after death. Spirit (soul) is the collective term for spirit and spirit (ghost).</v>
       </c>
       <c r="E13" t="str">
-        <v>吴氏灵体档案拍摄时，灵体（鬼魂）有时被称作”鬼“或者”灵魂“，但在2025年拍摄的吴氏灵魂医学中，灵体”鬼魂“的叫法被正式确立</v>
+        <v>吴氏灵体档案拍摄时，「灵体」、「鬼魂」、「灵魂」三个概念未做严格区分，是混淆在一起的。在2025年拍摄的吴氏灵魂医学中，上述三个概念被正式定义。「灵体」是指人活着时候的灵魂躯体。「鬼魂」是指人死后，从肉体中分离出来的、独立的灵魂生命。「灵魂」是对「灵体」和「鬼魂」的统称。</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -758,7 +758,7 @@
         <v>FILE 1-1-1</v>
       </c>
       <c r="E16" t="str">
-        <v>1-1-1系列</v>
+        <v>1-1-1档案</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -850,7 +850,7 @@
         <v>FILE 1-1-2</v>
       </c>
       <c r="E20" t="str">
-        <v>1-1-2系列</v>
+        <v>1-1-2档案</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -873,7 +873,7 @@
         <v>Scientifically prove the Existence of Souls through Epilepsy</v>
       </c>
       <c r="E21" t="str">
-        <v>如何用仪器科学地证明鬼魂真实的存在</v>
+        <v>如何设计脑电图实验以科学性验证灵体的存在</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -896,7 +896,7 @@
         <v>Demonstrating how EEG experiments can be applied to prove the existence of spirits ghosts</v>
       </c>
       <c r="E22" t="str">
-        <v>阐明如何设计脑电图实验以科学验证灵体的存在</v>
+        <v>如何设计脑电图实验以科学性验证灵体的存在</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -942,7 +942,7 @@
         <v>FILE 1-1-3</v>
       </c>
       <c r="E24" t="str">
-        <v>1-1-3系列</v>
+        <v>1-1-3档案</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -1057,7 +1057,7 @@
         <v>FILE 1-2-1</v>
       </c>
       <c r="E29" t="str">
-        <v>1-2-1系列</v>
+        <v>1-2-1档案</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -1173,7 +1173,7 @@
         <v>FILE 1-2-2</v>
       </c>
       <c r="E34" t="str">
-        <v>1-2-2系列</v>
+        <v>1-2-2档案</v>
       </c>
       <c r="F34" t="str">
         <v/>
@@ -1288,7 +1288,7 @@
         <v>FILE 1-2-3</v>
       </c>
       <c r="E39" t="str">
-        <v>1-2-3系列</v>
+        <v>1-2-3档案</v>
       </c>
       <c r="F39" t="str">
         <v/>
@@ -1403,7 +1403,7 @@
         <v>FILE 1-2-4</v>
       </c>
       <c r="E44" t="str">
-        <v>1-2-4系列</v>
+        <v>1-2-4档案</v>
       </c>
       <c r="F44" t="str">
         <v/>
@@ -1518,7 +1518,7 @@
         <v>FILE 1-2-5</v>
       </c>
       <c r="E49" t="str">
-        <v>1-2-5系列</v>
+        <v>1-2-5档案</v>
       </c>
       <c r="F49" t="str">
         <v/>
@@ -1633,7 +1633,7 @@
         <v>FILE 1-2-6</v>
       </c>
       <c r="E54" t="str">
-        <v>1-2-6系列</v>
+        <v>1-2-6档案</v>
       </c>
       <c r="F54" t="str">
         <v/>
@@ -1748,7 +1748,7 @@
         <v>FILE 1-3</v>
       </c>
       <c r="E59" t="str">
-        <v>1-3系列</v>
+        <v>1-3档案</v>
       </c>
       <c r="F59" t="str">
         <v/>
@@ -1865,7 +1865,7 @@
         <v>FILE 1-4</v>
       </c>
       <c r="E64" t="str">
-        <v>1-4系列</v>
+        <v>1-4档案</v>
       </c>
       <c r="F64" t="str">
         <v/>
@@ -1966,9 +1966,124 @@
         <v>siteContent.recordOfSoul</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>siteContent.recordOfSoul.filePageTitle</v>
+      </c>
+      <c r="B69" t="str">
+        <v>灵魂档案 / 档案页标题</v>
+      </c>
+      <c r="C69" t="str">
+        <v>heading</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Wu's Spirit File Page</v>
+      </c>
+      <c r="E69" t="str">
+        <v>吴氏灵体档案页</v>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v>siteContent.recordOfSoul</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>siteContent.recordOfSoul.terminologyExplanation</v>
+      </c>
+      <c r="B70" t="str">
+        <v>灵魂档案 / 术语说明</v>
+      </c>
+      <c r="C70" t="str">
+        <v>paragraph / other</v>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v>siteContent.recordOfSoul</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>record.footerBrand</v>
+      </c>
+      <c r="B71" t="str">
+        <v>灵魂档案 / i18n</v>
+      </c>
+      <c r="C71" t="str">
+        <v>label</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Wu's Spirit Files</v>
+      </c>
+      <c r="E71" t="str">
+        <v>吴氏灵体档案</v>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>record.videoCatalog</v>
+      </c>
+      <c r="B72" t="str">
+        <v>灵魂档案 / i18n</v>
+      </c>
+      <c r="C72" t="str">
+        <v>label</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Video catalog</v>
+      </c>
+      <c r="E72" t="str">
+        <v>视频目录</v>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>common.delete</v>
+      </c>
+      <c r="B73" t="str">
+        <v>灵魂档案 / i18n</v>
+      </c>
+      <c r="C73" t="str">
+        <v>label</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Delete</v>
+      </c>
+      <c r="E73" t="str">
+        <v>删除</v>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G68"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G73"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/page-copy/04-视频目录-灵魂档案.xlsx
+++ b/docs/page-copy/04-视频目录-灵魂档案.xlsx
@@ -1977,7 +1977,7 @@
         <v>heading</v>
       </c>
       <c r="D69" t="str">
-        <v>Wu's Spirit File Page</v>
+        <v>Woos record of soul Page</v>
       </c>
       <c r="E69" t="str">
         <v>吴氏灵体档案页</v>
